--- a/tools/mayan_sync_helper/xml_definitions/doc_metadata.xlsx
+++ b/tools/mayan_sync_helper/xml_definitions/doc_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Development\pims\PSP\tools\mayan_sync_helper\xml_definitions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SueT\projects\PSP\tools\mayan_sync_helper\xml_definitions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18655A55-99BF-496A-9DCC-AD18CE667633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FF9788-3489-4619-8914-393A4B52DDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26220" yWindow="2535" windowWidth="21990" windowHeight="16725" xr2:uid="{CBC9441C-C803-4FDD-A18E-69050E2FB6D7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CBC9441C-C803-4FDD-A18E-69050E2FB6D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="119">
   <si>
     <t>PID</t>
   </si>
@@ -372,6 +372,27 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>LETINTENT</t>
+  </si>
+  <si>
+    <t>LISTAGRMT</t>
+  </si>
+  <si>
+    <t>UTILBILL</t>
+  </si>
+  <si>
+    <t>WAIVECONDS</t>
+  </si>
+  <si>
+    <t>LTO_PLAN</t>
+  </si>
+  <si>
+    <t>LEGAL_DESCRIPTION</t>
+  </si>
+  <si>
+    <t>TERMOFFER</t>
   </si>
 </sst>
 </file>
@@ -454,19 +475,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,10 +572,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90DE8360-DBFA-4B01-BC17-8CB91A6450BA}" name="Table1" displayName="Table1" ref="B2:D119" totalsRowShown="0" tableBorderDxfId="3" totalsRowBorderDxfId="2" headerRowCellStyle="Normal">
-  <autoFilter ref="B2:D119" xr:uid="{90DE8360-DBFA-4B01-BC17-8CB91A6450BA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D119">
-    <sortCondition ref="C10:C119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90DE8360-DBFA-4B01-BC17-8CB91A6450BA}" name="Table1" displayName="Table1" ref="B2:D127" totalsRowShown="0" tableBorderDxfId="3" totalsRowBorderDxfId="2" headerRowCellStyle="Normal">
+  <autoFilter ref="B2:D127" xr:uid="{90DE8360-DBFA-4B01-BC17-8CB91A6450BA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D127">
+    <sortCondition ref="C10:C127"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{15654819-3967-43A9-B023-EBBA1E5CA728}" name="Document Type" dataDxfId="1"/>
@@ -864,1316 +883,1402 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42AC0DE-777F-4C37-A5EE-8BFCCB0EA9AB}">
-  <dimension ref="B2:E119"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:E127"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="3"/>
-    <col min="2" max="2" width="22.90625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B28" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="1" t="s">
+      <c r="D32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B33" s="1" t="s">
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B35" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="D41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B43" s="1" t="s">
+      <c r="D44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B45" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B47" s="1" t="s">
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B48" s="1" t="s">
+      <c r="D49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B49" s="1" t="s">
+      <c r="D50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B50" s="1" t="s">
+      <c r="D51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B54" s="1" t="s">
+      <c r="D55" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B55" s="1" t="s">
+      <c r="D56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B56" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B57" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B61" s="1" t="s">
+      <c r="D62" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B62" s="1" t="s">
+      <c r="D63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B63" s="1" t="s">
+      <c r="D64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B64" s="1" t="s">
+      <c r="D66" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B66" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D67" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D68" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D69" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="s">
+      <c r="D73" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B72" s="1" t="s">
+      <c r="D74" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B73" s="1" t="s">
+      <c r="C76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D76" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D78" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
+      <c r="C79" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B75" s="1" t="s">
+      <c r="C80" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B76" s="1" t="s">
+      <c r="C81" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D81" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B77" s="1" t="s">
+      <c r="C82" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B78" s="1" t="s">
+      <c r="C83" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B79" s="1" t="s">
+      <c r="C84" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D84" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B80" s="1" t="s">
+      <c r="C85" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B81" s="1" t="s">
+      <c r="C86" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B82" s="1" t="s">
+      <c r="C87" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D87" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B83" s="1" t="s">
+      <c r="C88" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B84" s="1" t="s">
+      <c r="C89" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B85" s="1" t="s">
+      <c r="C90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B86" s="1" t="s">
+      <c r="C91" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B87" s="1" t="s">
+      <c r="C92" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D92" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B88" s="1" t="s">
+      <c r="C93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D93" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="C94" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B90" s="1" t="s">
+      <c r="C95" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D95" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B91" s="1" t="s">
+      <c r="C96" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D96" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B92" s="1" t="s">
+      <c r="C97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B93" s="1" t="s">
+      <c r="C98" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D99" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+      <c r="C100" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B95" s="1" t="s">
+      <c r="C102" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B96" s="1" t="s">
+      <c r="C103" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B97" s="1" t="s">
+      <c r="C104" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D104" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B98" s="1" t="s">
+      <c r="C105" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D105" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B99" s="1" t="s">
+      <c r="C106" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D106" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B100" s="1" t="s">
+      <c r="C107" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B101" s="1" t="s">
+      <c r="C108" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D108" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B102" s="1" t="s">
+      <c r="C109" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D109" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B103" s="1" t="s">
+      <c r="C110" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D110" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B104" s="1" t="s">
+      <c r="C111" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B105" s="1" t="s">
+      <c r="C112" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B106" s="1" t="s">
+      <c r="C113" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B107" s="1" t="s">
+      <c r="C114" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D114" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B108" s="1" t="s">
+      <c r="C115" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D115" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B109" s="1" t="s">
+      <c r="C116" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D116" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B110" s="1" t="s">
+      <c r="C117" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D117" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B118" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B111" s="1" t="s">
+      <c r="C118" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D118" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B112" s="1" t="s">
+      <c r="C119" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D119" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B113" s="1" t="s">
+      <c r="C120" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D120" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B114" s="1" t="s">
+      <c r="D121" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B122" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B115" s="1" t="s">
+      <c r="D122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B116" s="1" t="s">
+      <c r="D123" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B117" s="1" t="s">
+      <c r="D124" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B118" s="1" t="s">
+      <c r="D125" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B119" s="5" t="s">
+      <c r="D126" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B127" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C119" s="6"/>
+      <c r="C127" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E120">
-    <sortCondition ref="E4:E120"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E128">
+    <sortCondition ref="E4:E128"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2187,7 +2292,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EBA357-ECF0-4B18-8001-63126409DF6A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
